--- a/internal_doc/05.测试设计/sdv/覆盖安装OM/coverinstallOM.xlsx
+++ b/internal_doc/05.测试设计/sdv/覆盖安装OM/coverinstallOM.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -108,12 +108,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1.执行run包，安装OM
-2.停止sdbcm/sdbom进程 service sdbcm stop
-3.覆盖安装OM</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>停止sdbcm进程，删除om配置文件的情况下，覆盖安装om</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -122,6 +116,16 @@
 2.删除om的配置文件./sequoiadb/conf/local/..
 3.停止sdbcm进程 kill PID
 4.覆盖安装OM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1.执行run包，安装OM
+2.停止sdbcm/sdbom进程 service sdbcm stop
+3.覆盖安装OM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、覆盖安装OM失败，打印错误信息：创建OM失败</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -734,7 +738,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>20</v>
@@ -745,7 +749,7 @@
     </row>
     <row r="5" spans="1:9" ht="30" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -759,10 +763,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I5" s="2">
         <v>1</v>
